--- a/assets/tour-2027-numbers.xlsx
+++ b/assets/tour-2027-numbers.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/regulocastrogomez/Downloads/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{1E2508DD-5E53-1A49-B157-906974A97B8C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{650DCAA3-FACB-E049-B673-D2D627B5A89F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="380" yWindow="600" windowWidth="28040" windowHeight="16660" xr2:uid="{BBF3B1B2-2BD0-D242-B940-7BB9A5C7F668}"/>
   </bookViews>
@@ -347,7 +347,7 @@
     <t xml:space="preserve">*Note cost in USD </t>
   </si>
   <si>
-    <t>16 tours - 94 cities in total</t>
+    <t>16 tours - 92 cities in total</t>
   </si>
 </sst>
 </file>

--- a/assets/tour-2027-numbers.xlsx
+++ b/assets/tour-2027-numbers.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/regulocastrogomez/Downloads/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{650DCAA3-FACB-E049-B673-D2D627B5A89F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{86321418-ED0D-7648-A2A6-C757493927C5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="380" yWindow="600" windowWidth="28040" windowHeight="16660" xr2:uid="{BBF3B1B2-2BD0-D242-B940-7BB9A5C7F668}"/>
   </bookViews>
@@ -39,7 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="131" uniqueCount="103">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="132" uniqueCount="104">
   <si>
     <t>CD. JUAREZ</t>
   </si>
@@ -348,6 +348,9 @@
   </si>
   <si>
     <t>16 tours - 92 cities in total</t>
+  </si>
+  <si>
+    <t>AUGUST</t>
   </si>
 </sst>
 </file>
@@ -1935,7 +1938,9 @@
       <c r="A88" s="8" t="s">
         <v>80</v>
       </c>
-      <c r="B88" s="9"/>
+      <c r="B88" s="32" t="s">
+        <v>103</v>
+      </c>
       <c r="C88" s="9"/>
       <c r="D88" s="28"/>
     </row>
